--- a/tippmix.xlsx
+++ b/tippmix.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="66">
   <si>
     <t>♠  TIPPMIX BANKROLL MANAGER  ♠</t>
   </si>
@@ -74,9 +74,6 @@
   </si>
   <si>
     <t>Veszített</t>
-  </si>
-  <si>
-    <t>Függőben</t>
   </si>
   <si>
     <t>♠  TIPPMIX – HAVI ELEMZÉS</t>
@@ -3354,7 +3351,7 @@
         <f>IF(OR(E73="",D73=""),"",E73*D73)</f>
       </c>
       <c r="G73" s="21" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H73" s="20">
         <f>IF(G73="Nyert",F73,0)</f>
@@ -4181,7 +4178,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -4193,22 +4190,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D59)</f>
@@ -4224,7 +4221,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O4" s="44">
         <f>SUM(H7:H59)</f>
@@ -4240,7 +4237,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O5" s="44">
         <f>SUM(I7:I59)</f>
@@ -4249,16 +4246,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="C6" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="32" t="s">
-        <v>36</v>
-      </c>
       <c r="D6" s="32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -4267,26 +4264,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I6" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="32" t="s">
-        <v>31</v>
-      </c>
       <c r="L6" s="29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>
@@ -6555,7 +6552,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6569,7 +6566,7 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="50">
         <f>SUM('Tippmix napló'!I7:I133)</f>
@@ -6580,7 +6577,7 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)</f>
@@ -6591,7 +6588,7 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))</f>
@@ -6602,7 +6599,7 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B6" s="51">
         <f>IFERROR(COUNTIF('Tippmix napló'!G7:G133,"Nyert")/(COUNTIF('Tippmix napló'!G7:G133,"Nyert")+COUNTIF('Tippmix napló'!G7:G133,"Veszített")),0)</f>
@@ -6613,7 +6610,7 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="49" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B7" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)),0)</f>
@@ -6624,7 +6621,7 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="49" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B8" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))),0)</f>
@@ -6665,7 +6662,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6683,13 +6680,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B3" s="53" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -6697,13 +6694,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="52" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B4" s="53" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -6711,13 +6708,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="52" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="53" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="C5" s="54" t="s">
         <v>51</v>
-      </c>
-      <c r="C5" s="54" t="s">
-        <v>52</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -6725,13 +6722,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="52" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" s="53" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -6739,13 +6736,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="52" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B7" s="53" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -6753,13 +6750,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="52" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B8" s="53" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -6767,13 +6764,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="53" t="s">
+      <c r="C9" s="54" t="s">
         <v>60</v>
-      </c>
-      <c r="C9" s="54" t="s">
-        <v>61</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -6789,22 +6786,22 @@
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="55" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="55" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="55" t="s">
+      <c r="C12" s="56" t="s">
         <v>63</v>
-      </c>
-      <c r="C12" s="56" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="13" ht="105" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="55"/>
       <c r="B13" s="55" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="56" t="s">
         <v>65</v>
-      </c>
-      <c r="C13" s="56" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -6846,7 +6843,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6858,22 +6855,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="29" t="s">
         <v>21</v>
-      </c>
-      <c r="L3" s="29" t="s">
-        <v>22</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D18)</f>
@@ -6889,7 +6886,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O4" s="31">
         <f>SUM(H7:H18)</f>
@@ -6905,7 +6902,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O5" s="31">
         <f>SUM(I7:I18)</f>
@@ -6914,16 +6911,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="C6" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="32" t="s">
-        <v>27</v>
-      </c>
       <c r="D6" s="32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -6932,26 +6929,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="32" t="s">
+      <c r="I6" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="32" t="s">
+      <c r="J6" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="32" t="s">
-        <v>31</v>
-      </c>
       <c r="L6" s="29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>

--- a/tippmix.xlsx
+++ b/tippmix.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="67">
   <si>
     <t>♠  TIPPMIX BANKROLL MANAGER  ♠</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t>Veszített</t>
+  </si>
+  <si>
+    <t>Függőben</t>
   </si>
   <si>
     <t>♠  TIPPMIX – HAVI ELEMZÉS</t>
@@ -3402,13 +3405,33 @@
     <row r="75" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
-      <c r="C75" s="17"/>
-      <c r="D75" s="18"/>
-      <c r="E75" s="19"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="21"/>
-      <c r="H75" s="20"/>
-      <c r="I75" s="22"/>
+      <c r="C75" s="17">
+        <v>46323.5</v>
+      </c>
+      <c r="D75" s="18">
+        <v>2000</v>
+      </c>
+      <c r="E75" s="19">
+        <v>2.33</v>
+      </c>
+      <c r="F75" s="20">
+        <f>IF(OR(E75="",D75=""),"",E75*D75)</f>
+      </c>
+      <c r="G75" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="H75" s="20">
+        <f>IF(G75="Nyert",F75,0)</f>
+      </c>
+      <c r="I75" s="22">
+        <f>IF(G75="Nyert",H75-D75,IF(G75="Veszített",-D75,0))</f>
+      </c>
+      <c r="J75" t="s">
+        <v>15</v>
+      </c>
+      <c r="K75" t="s">
+        <v>15</v>
+      </c>
       <c r="L75" s="1"/>
     </row>
     <row r="76" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -4178,7 +4201,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -4190,22 +4213,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D59)</f>
@@ -4221,7 +4244,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O4" s="44">
         <f>SUM(H7:H59)</f>
@@ -4237,7 +4260,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O5" s="44">
         <f>SUM(I7:I59)</f>
@@ -4246,16 +4269,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -4264,26 +4287,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J6" s="32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>
@@ -6552,7 +6575,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6566,7 +6589,7 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="49" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="50">
         <f>SUM('Tippmix napló'!I7:I133)</f>
@@ -6577,7 +6600,7 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="49" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)</f>
@@ -6588,7 +6611,7 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="49" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))</f>
@@ -6599,7 +6622,7 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="49" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6" s="51">
         <f>IFERROR(COUNTIF('Tippmix napló'!G7:G133,"Nyert")/(COUNTIF('Tippmix napló'!G7:G133,"Nyert")+COUNTIF('Tippmix napló'!G7:G133,"Veszített")),0)</f>
@@ -6610,7 +6633,7 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="49" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)),0)</f>
@@ -6621,7 +6644,7 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="49" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))),0)</f>
@@ -6662,7 +6685,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6680,13 +6703,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B3" s="53" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -6694,13 +6717,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="52" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B4" s="53" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -6708,13 +6731,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="52" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -6722,13 +6745,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="52" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" s="53" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -6736,13 +6759,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="52" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B7" s="53" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -6750,13 +6773,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="52" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B8" s="53" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -6764,13 +6787,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="52" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C9" s="54" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -6786,22 +6809,22 @@
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="55" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B12" s="55" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C12" s="56" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" ht="105" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="55"/>
       <c r="B13" s="55" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C13" s="56" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -6843,7 +6866,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6855,22 +6878,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D18)</f>
@@ -6886,7 +6909,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O4" s="31">
         <f>SUM(H7:H18)</f>
@@ -6902,7 +6925,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O5" s="31">
         <f>SUM(I7:I18)</f>
@@ -6911,16 +6934,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -6929,26 +6952,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H6" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="L6" s="29" t="s">
         <v>28</v>
-      </c>
-      <c r="I6" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="29" t="s">
-        <v>27</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>

--- a/tippmix.xlsx
+++ b/tippmix.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="66">
   <si>
     <t>♠  TIPPMIX BANKROLL MANAGER  ♠</t>
   </si>
@@ -74,9 +74,6 @@
   </si>
   <si>
     <t>Veszített</t>
-  </si>
-  <si>
-    <t>Függőben</t>
   </si>
   <si>
     <t>♠  TIPPMIX – HAVI ELEMZÉS</t>
@@ -3418,7 +3415,7 @@
         <f>IF(OR(E75="",D75=""),"",E75*D75)</f>
       </c>
       <c r="G75" s="21" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H75" s="20">
         <f>IF(G75="Nyert",F75,0)</f>
@@ -4201,7 +4198,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -4213,22 +4210,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D59)</f>
@@ -4244,7 +4241,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O4" s="44">
         <f>SUM(H7:H59)</f>
@@ -4260,7 +4257,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O5" s="44">
         <f>SUM(I7:I59)</f>
@@ -4269,16 +4266,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="C6" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="32" t="s">
-        <v>36</v>
-      </c>
       <c r="D6" s="32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -4287,26 +4284,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I6" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="32" t="s">
-        <v>31</v>
-      </c>
       <c r="L6" s="29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>
@@ -6575,7 +6572,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6589,7 +6586,7 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="50">
         <f>SUM('Tippmix napló'!I7:I133)</f>
@@ -6600,7 +6597,7 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)</f>
@@ -6611,7 +6608,7 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))</f>
@@ -6622,7 +6619,7 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B6" s="51">
         <f>IFERROR(COUNTIF('Tippmix napló'!G7:G133,"Nyert")/(COUNTIF('Tippmix napló'!G7:G133,"Nyert")+COUNTIF('Tippmix napló'!G7:G133,"Veszített")),0)</f>
@@ -6633,7 +6630,7 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="49" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B7" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)),0)</f>
@@ -6644,7 +6641,7 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="49" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B8" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))),0)</f>
@@ -6685,7 +6682,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6703,13 +6700,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B3" s="53" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -6717,13 +6714,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="52" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B4" s="53" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -6731,13 +6728,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="52" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="53" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="C5" s="54" t="s">
         <v>51</v>
-      </c>
-      <c r="C5" s="54" t="s">
-        <v>52</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -6745,13 +6742,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="52" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" s="53" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -6759,13 +6756,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="52" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B7" s="53" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -6773,13 +6770,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="52" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B8" s="53" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -6787,13 +6784,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="53" t="s">
+      <c r="C9" s="54" t="s">
         <v>60</v>
-      </c>
-      <c r="C9" s="54" t="s">
-        <v>61</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -6809,22 +6806,22 @@
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="55" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="55" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="55" t="s">
+      <c r="C12" s="56" t="s">
         <v>63</v>
-      </c>
-      <c r="C12" s="56" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="13" ht="105" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="55"/>
       <c r="B13" s="55" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="56" t="s">
         <v>65</v>
-      </c>
-      <c r="C13" s="56" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -6866,7 +6863,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6878,22 +6875,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="29" t="s">
         <v>21</v>
-      </c>
-      <c r="L3" s="29" t="s">
-        <v>22</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D18)</f>
@@ -6909,7 +6906,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O4" s="31">
         <f>SUM(H7:H18)</f>
@@ -6925,7 +6922,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O5" s="31">
         <f>SUM(I7:I18)</f>
@@ -6934,16 +6931,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="C6" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="32" t="s">
-        <v>27</v>
-      </c>
       <c r="D6" s="32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -6952,26 +6949,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="32" t="s">
+      <c r="I6" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="32" t="s">
+      <c r="J6" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="32" t="s">
-        <v>31</v>
-      </c>
       <c r="L6" s="29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>

--- a/tippmix.xlsx
+++ b/tippmix.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="67">
   <si>
     <t>♠  TIPPMIX BANKROLL MANAGER  ♠</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t>Veszített</t>
+  </si>
+  <si>
+    <t>Függőben</t>
   </si>
   <si>
     <t>♠  TIPPMIX – HAVI ELEMZÉS</t>
@@ -3415,7 +3418,7 @@
         <f>IF(OR(E75="",D75=""),"",E75*D75)</f>
       </c>
       <c r="G75" s="21" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H75" s="20">
         <f>IF(G75="Nyert",F75,0)</f>
@@ -4198,7 +4201,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -4210,22 +4213,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D59)</f>
@@ -4241,7 +4244,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O4" s="44">
         <f>SUM(H7:H59)</f>
@@ -4257,7 +4260,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O5" s="44">
         <f>SUM(I7:I59)</f>
@@ -4266,16 +4269,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -4284,26 +4287,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J6" s="32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>
@@ -6572,7 +6575,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6586,7 +6589,7 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="49" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="50">
         <f>SUM('Tippmix napló'!I7:I133)</f>
@@ -6597,7 +6600,7 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="49" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)</f>
@@ -6608,7 +6611,7 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="49" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))</f>
@@ -6619,7 +6622,7 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="49" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6" s="51">
         <f>IFERROR(COUNTIF('Tippmix napló'!G7:G133,"Nyert")/(COUNTIF('Tippmix napló'!G7:G133,"Nyert")+COUNTIF('Tippmix napló'!G7:G133,"Veszített")),0)</f>
@@ -6630,7 +6633,7 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="49" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)),0)</f>
@@ -6641,7 +6644,7 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="49" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))),0)</f>
@@ -6682,7 +6685,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6700,13 +6703,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B3" s="53" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -6714,13 +6717,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="52" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B4" s="53" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -6728,13 +6731,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="52" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -6742,13 +6745,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="52" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" s="53" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -6756,13 +6759,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="52" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B7" s="53" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -6770,13 +6773,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="52" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B8" s="53" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -6784,13 +6787,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="52" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C9" s="54" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -6806,22 +6809,22 @@
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="55" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B12" s="55" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C12" s="56" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" ht="105" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="55"/>
       <c r="B13" s="55" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C13" s="56" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -6863,7 +6866,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6875,22 +6878,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D18)</f>
@@ -6906,7 +6909,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O4" s="31">
         <f>SUM(H7:H18)</f>
@@ -6922,7 +6925,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O5" s="31">
         <f>SUM(I7:I18)</f>
@@ -6931,16 +6934,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -6949,26 +6952,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H6" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="L6" s="29" t="s">
         <v>28</v>
-      </c>
-      <c r="I6" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="29" t="s">
-        <v>27</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>

--- a/tippmix.xlsx
+++ b/tippmix.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="66">
   <si>
     <t>♠  TIPPMIX BANKROLL MANAGER  ♠</t>
   </si>
@@ -3338,33 +3338,13 @@
     <row r="73" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
-      <c r="C73" s="17">
-        <v>46321.5</v>
-      </c>
-      <c r="D73" s="18">
-        <v>2000</v>
-      </c>
-      <c r="E73" s="19">
-        <v>2.59</v>
-      </c>
-      <c r="F73" s="20">
-        <f>IF(OR(E73="",D73=""),"",E73*D73)</f>
-      </c>
-      <c r="G73" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H73" s="20">
-        <f>IF(G73="Nyert",F73,0)</f>
-      </c>
-      <c r="I73" s="22">
-        <f>IF(G73="Nyert",H73-D73,IF(G73="Veszített",-D73,0))</f>
-      </c>
-      <c r="J73" t="s">
-        <v>15</v>
-      </c>
-      <c r="K73" t="s">
-        <v>15</v>
-      </c>
+      <c r="C73" s="17"/>
+      <c r="D73" s="18"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="20"/>
+      <c r="G73" s="21"/>
+      <c r="H73" s="20"/>
+      <c r="I73" s="22"/>
       <c r="L73" s="1"/>
     </row>
     <row r="74" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">

--- a/tippmix.xlsx
+++ b/tippmix.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="66">
   <si>
     <t>♠  TIPPMIX BANKROLL MANAGER  ♠</t>
   </si>
@@ -3338,13 +3338,33 @@
     <row r="73" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
-      <c r="C73" s="17"/>
-      <c r="D73" s="18"/>
-      <c r="E73" s="19"/>
-      <c r="F73" s="20"/>
-      <c r="G73" s="21"/>
-      <c r="H73" s="20"/>
-      <c r="I73" s="22"/>
+      <c r="C73" s="17">
+        <v>46321.5</v>
+      </c>
+      <c r="D73" s="18">
+        <v>2000</v>
+      </c>
+      <c r="E73" s="19">
+        <v>2.59</v>
+      </c>
+      <c r="F73" s="20">
+        <f>IF(OR(E73="",D73=""),"",E73*D73)</f>
+      </c>
+      <c r="G73" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="H73" s="20">
+        <f>IF(G73="Nyert",F73,0)</f>
+      </c>
+      <c r="I73" s="22">
+        <f>IF(G73="Nyert",H73-D73,IF(G73="Veszített",-D73,0))</f>
+      </c>
+      <c r="J73" t="s">
+        <v>15</v>
+      </c>
+      <c r="K73" t="s">
+        <v>15</v>
+      </c>
       <c r="L73" s="1"/>
     </row>
     <row r="74" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">

--- a/tippmix.xlsx
+++ b/tippmix.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="66">
   <si>
     <t>♠  TIPPMIX BANKROLL MANAGER  ♠</t>
   </si>
@@ -3370,13 +3370,33 @@
     <row r="74" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
-      <c r="C74" s="17"/>
-      <c r="D74" s="18"/>
-      <c r="E74" s="19"/>
-      <c r="F74" s="23"/>
-      <c r="G74" s="21"/>
-      <c r="H74" s="23"/>
-      <c r="I74" s="22"/>
+      <c r="C74" s="17">
+        <v>46322.5</v>
+      </c>
+      <c r="D74" s="18">
+        <v>2000</v>
+      </c>
+      <c r="E74" s="19">
+        <v>2.55</v>
+      </c>
+      <c r="F74" s="23">
+        <f>IF(OR(E74="",D74=""),"",E74*D74)</f>
+      </c>
+      <c r="G74" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="H74" s="23">
+        <f>IF(G74="Nyert",F74,0)</f>
+      </c>
+      <c r="I74" s="22">
+        <f>IF(G74="Nyert",H74-D74,IF(G74="Veszített",-D74,0))</f>
+      </c>
+      <c r="J74" t="s">
+        <v>15</v>
+      </c>
+      <c r="K74" t="s">
+        <v>15</v>
+      </c>
       <c r="L74" s="1"/>
     </row>
     <row r="75" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">

--- a/tippmix.xlsx
+++ b/tippmix.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="67">
   <si>
     <t>♠  TIPPMIX BANKROLL MANAGER  ♠</t>
   </si>
@@ -3437,13 +3437,33 @@
     <row r="76" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
-      <c r="C76" s="17"/>
-      <c r="D76" s="18"/>
-      <c r="E76" s="19"/>
-      <c r="F76" s="23"/>
-      <c r="G76" s="21"/>
-      <c r="H76" s="23"/>
-      <c r="I76" s="22"/>
+      <c r="C76" s="17">
+        <v>46327.5</v>
+      </c>
+      <c r="D76" s="18">
+        <v>1000</v>
+      </c>
+      <c r="E76" s="19">
+        <v>2</v>
+      </c>
+      <c r="F76" s="23">
+        <f>IF(OR(E76="",D76=""),"",E76*D76)</f>
+      </c>
+      <c r="G76" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="H76" s="23">
+        <f>IF(G76="Nyert",F76,0)</f>
+      </c>
+      <c r="I76" s="22">
+        <f>IF(G76="Nyert",H76-D76,IF(G76="Veszített",-D76,0))</f>
+      </c>
+      <c r="J76" t="s">
+        <v>15</v>
+      </c>
+      <c r="K76" t="s">
+        <v>15</v>
+      </c>
       <c r="L76" s="1"/>
     </row>
     <row r="77" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">

--- a/tippmix.xlsx
+++ b/tippmix.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="67">
   <si>
     <t>♠  TIPPMIX BANKROLL MANAGER  ♠</t>
   </si>
@@ -3437,33 +3437,13 @@
     <row r="76" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
-      <c r="C76" s="17">
-        <v>46327.5</v>
-      </c>
-      <c r="D76" s="18">
-        <v>1000</v>
-      </c>
-      <c r="E76" s="19">
-        <v>2</v>
-      </c>
-      <c r="F76" s="23">
-        <f>IF(OR(E76="",D76=""),"",E76*D76)</f>
-      </c>
-      <c r="G76" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H76" s="23">
-        <f>IF(G76="Nyert",F76,0)</f>
-      </c>
-      <c r="I76" s="22">
-        <f>IF(G76="Nyert",H76-D76,IF(G76="Veszített",-D76,0))</f>
-      </c>
-      <c r="J76" t="s">
-        <v>15</v>
-      </c>
-      <c r="K76" t="s">
-        <v>15</v>
-      </c>
+      <c r="C76" s="17"/>
+      <c r="D76" s="18"/>
+      <c r="E76" s="19"/>
+      <c r="F76" s="23"/>
+      <c r="G76" s="21"/>
+      <c r="H76" s="23"/>
+      <c r="I76" s="22"/>
       <c r="L76" s="1"/>
     </row>
     <row r="77" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">

--- a/tippmix.xlsx
+++ b/tippmix.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="66">
   <si>
     <t>♠  TIPPMIX BANKROLL MANAGER  ♠</t>
   </si>
@@ -74,9 +74,6 @@
   </si>
   <si>
     <t>Veszített</t>
-  </si>
-  <si>
-    <t>Függőben</t>
   </si>
   <si>
     <t>♠  TIPPMIX – HAVI ELEMZÉS</t>
@@ -3418,7 +3415,7 @@
         <f>IF(OR(E75="",D75=""),"",E75*D75)</f>
       </c>
       <c r="G75" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H75" s="20">
         <f>IF(G75="Nyert",F75,0)</f>
@@ -4201,7 +4198,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -4213,22 +4210,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D59)</f>
@@ -4244,7 +4241,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O4" s="44">
         <f>SUM(H7:H59)</f>
@@ -4260,7 +4257,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O5" s="44">
         <f>SUM(I7:I59)</f>
@@ -4269,16 +4266,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="C6" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="32" t="s">
-        <v>36</v>
-      </c>
       <c r="D6" s="32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -4287,26 +4284,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I6" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="32" t="s">
-        <v>31</v>
-      </c>
       <c r="L6" s="29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>
@@ -6575,7 +6572,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6589,7 +6586,7 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="50">
         <f>SUM('Tippmix napló'!I7:I133)</f>
@@ -6600,7 +6597,7 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)</f>
@@ -6611,7 +6608,7 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))</f>
@@ -6622,7 +6619,7 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B6" s="51">
         <f>IFERROR(COUNTIF('Tippmix napló'!G7:G133,"Nyert")/(COUNTIF('Tippmix napló'!G7:G133,"Nyert")+COUNTIF('Tippmix napló'!G7:G133,"Veszített")),0)</f>
@@ -6633,7 +6630,7 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="49" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B7" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)),0)</f>
@@ -6644,7 +6641,7 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="49" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B8" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))),0)</f>
@@ -6685,7 +6682,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6703,13 +6700,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B3" s="53" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -6717,13 +6714,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="52" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B4" s="53" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -6731,13 +6728,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="52" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="53" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="C5" s="54" t="s">
         <v>51</v>
-      </c>
-      <c r="C5" s="54" t="s">
-        <v>52</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -6745,13 +6742,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="52" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" s="53" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -6759,13 +6756,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="52" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B7" s="53" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -6773,13 +6770,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="52" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B8" s="53" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -6787,13 +6784,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="53" t="s">
+      <c r="C9" s="54" t="s">
         <v>60</v>
-      </c>
-      <c r="C9" s="54" t="s">
-        <v>61</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -6809,22 +6806,22 @@
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="55" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="55" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="55" t="s">
+      <c r="C12" s="56" t="s">
         <v>63</v>
-      </c>
-      <c r="C12" s="56" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="13" ht="105" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="55"/>
       <c r="B13" s="55" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="56" t="s">
         <v>65</v>
-      </c>
-      <c r="C13" s="56" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -6866,7 +6863,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6878,22 +6875,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="29" t="s">
         <v>21</v>
-      </c>
-      <c r="L3" s="29" t="s">
-        <v>22</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D18)</f>
@@ -6909,7 +6906,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O4" s="31">
         <f>SUM(H7:H18)</f>
@@ -6925,7 +6922,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O5" s="31">
         <f>SUM(I7:I18)</f>
@@ -6934,16 +6931,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="C6" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="32" t="s">
-        <v>27</v>
-      </c>
       <c r="D6" s="32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -6952,26 +6949,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="32" t="s">
+      <c r="I6" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="32" t="s">
+      <c r="J6" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="32" t="s">
-        <v>31</v>
-      </c>
       <c r="L6" s="29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>

--- a/tippmix.xlsx
+++ b/tippmix.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="67">
   <si>
     <t>♠  TIPPMIX BANKROLL MANAGER  ♠</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t>Veszített</t>
+  </si>
+  <si>
+    <t>Függőben</t>
   </si>
   <si>
     <t>♠  TIPPMIX – HAVI ELEMZÉS</t>
@@ -3434,13 +3437,33 @@
     <row r="76" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
-      <c r="C76" s="17"/>
-      <c r="D76" s="18"/>
-      <c r="E76" s="19"/>
-      <c r="F76" s="23"/>
-      <c r="G76" s="21"/>
-      <c r="H76" s="23"/>
-      <c r="I76" s="22"/>
+      <c r="C76" s="17">
+        <v>46324.5</v>
+      </c>
+      <c r="D76" s="18">
+        <v>2000</v>
+      </c>
+      <c r="E76" s="19">
+        <v>2.2</v>
+      </c>
+      <c r="F76" s="23">
+        <f>IF(OR(E76="",D76=""),"",E76*D76)</f>
+      </c>
+      <c r="G76" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="H76" s="23">
+        <f>IF(G76="Nyert",F76,0)</f>
+      </c>
+      <c r="I76" s="22">
+        <f>IF(G76="Nyert",H76-D76,IF(G76="Veszített",-D76,0))</f>
+      </c>
+      <c r="J76" t="s">
+        <v>15</v>
+      </c>
+      <c r="K76" t="s">
+        <v>15</v>
+      </c>
       <c r="L76" s="1"/>
     </row>
     <row r="77" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -4198,7 +4221,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -4210,22 +4233,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D59)</f>
@@ -4241,7 +4264,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O4" s="44">
         <f>SUM(H7:H59)</f>
@@ -4257,7 +4280,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O5" s="44">
         <f>SUM(I7:I59)</f>
@@ -4266,16 +4289,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -4284,26 +4307,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J6" s="32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>
@@ -6572,7 +6595,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6586,7 +6609,7 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="49" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="50">
         <f>SUM('Tippmix napló'!I7:I133)</f>
@@ -6597,7 +6620,7 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="49" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)</f>
@@ -6608,7 +6631,7 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="49" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))</f>
@@ -6619,7 +6642,7 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="49" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6" s="51">
         <f>IFERROR(COUNTIF('Tippmix napló'!G7:G133,"Nyert")/(COUNTIF('Tippmix napló'!G7:G133,"Nyert")+COUNTIF('Tippmix napló'!G7:G133,"Veszített")),0)</f>
@@ -6630,7 +6653,7 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="49" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)),0)</f>
@@ -6641,7 +6664,7 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="49" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))),0)</f>
@@ -6682,7 +6705,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6700,13 +6723,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B3" s="53" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -6714,13 +6737,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="52" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B4" s="53" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -6728,13 +6751,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="52" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -6742,13 +6765,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="52" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" s="53" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -6756,13 +6779,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="52" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B7" s="53" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -6770,13 +6793,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="52" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B8" s="53" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -6784,13 +6807,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="52" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C9" s="54" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -6806,22 +6829,22 @@
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="55" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B12" s="55" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C12" s="56" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" ht="105" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="55"/>
       <c r="B13" s="55" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C13" s="56" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -6863,7 +6886,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6875,22 +6898,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D18)</f>
@@ -6906,7 +6929,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O4" s="31">
         <f>SUM(H7:H18)</f>
@@ -6922,7 +6945,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O5" s="31">
         <f>SUM(I7:I18)</f>
@@ -6931,16 +6954,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -6949,26 +6972,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H6" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="L6" s="29" t="s">
         <v>28</v>
-      </c>
-      <c r="I6" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="29" t="s">
-        <v>27</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>

--- a/tippmix.xlsx
+++ b/tippmix.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="68">
   <si>
     <t>♠  TIPPMIX BANKROLL MANAGER  ♠</t>
   </si>
@@ -77,6 +77,9 @@
   </si>
   <si>
     <t>Függőben</t>
+  </si>
+  <si>
+    <t>psg - arsenal</t>
   </si>
   <si>
     <t>♠  TIPPMIX – HAVI ELEMZÉS</t>
@@ -3469,13 +3472,33 @@
     <row r="77" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
-      <c r="C77" s="17"/>
-      <c r="D77" s="18"/>
-      <c r="E77" s="19"/>
-      <c r="F77" s="20"/>
-      <c r="G77" s="21"/>
-      <c r="H77" s="20"/>
-      <c r="I77" s="22"/>
+      <c r="C77" s="17">
+        <v>46328.5</v>
+      </c>
+      <c r="D77" s="18">
+        <v>2000</v>
+      </c>
+      <c r="E77" s="19">
+        <v>2.5</v>
+      </c>
+      <c r="F77" s="20">
+        <f>IF(OR(E77="",D77=""),"",E77*D77)</f>
+      </c>
+      <c r="G77" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="H77" s="20">
+        <f>IF(G77="Nyert",F77,0)</f>
+      </c>
+      <c r="I77" s="22">
+        <f>IF(G77="Nyert",H77-D77,IF(G77="Veszített",-D77,0))</f>
+      </c>
+      <c r="J77" t="s">
+        <v>18</v>
+      </c>
+      <c r="K77" t="s">
+        <v>15</v>
+      </c>
       <c r="L77" s="1"/>
     </row>
     <row r="78" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -4221,7 +4244,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -4233,22 +4256,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D59)</f>
@@ -4264,7 +4287,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O4" s="44">
         <f>SUM(H7:H59)</f>
@@ -4280,7 +4303,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O5" s="44">
         <f>SUM(I7:I59)</f>
@@ -4289,16 +4312,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -4307,26 +4330,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J6" s="32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>
@@ -6595,7 +6618,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6609,7 +6632,7 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="49" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="50">
         <f>SUM('Tippmix napló'!I7:I133)</f>
@@ -6620,7 +6643,7 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="49" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)</f>
@@ -6631,7 +6654,7 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="49" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))</f>
@@ -6642,7 +6665,7 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="49" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" s="51">
         <f>IFERROR(COUNTIF('Tippmix napló'!G7:G133,"Nyert")/(COUNTIF('Tippmix napló'!G7:G133,"Nyert")+COUNTIF('Tippmix napló'!G7:G133,"Veszített")),0)</f>
@@ -6653,7 +6676,7 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="49" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)),0)</f>
@@ -6664,7 +6687,7 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="49" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))),0)</f>
@@ -6705,7 +6728,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6723,13 +6746,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B3" s="53" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -6737,13 +6760,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="52" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B4" s="53" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -6751,13 +6774,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="52" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -6765,13 +6788,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="52" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B6" s="53" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -6779,13 +6802,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="52" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B7" s="53" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -6793,13 +6816,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="52" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B8" s="53" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -6807,13 +6830,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="52" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9" s="54" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -6829,22 +6852,22 @@
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="55" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B12" s="55" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C12" s="56" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" ht="105" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="55"/>
       <c r="B13" s="55" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C13" s="56" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -6886,7 +6909,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6898,22 +6921,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D18)</f>
@@ -6929,7 +6952,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O4" s="31">
         <f>SUM(H7:H18)</f>
@@ -6945,7 +6968,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O5" s="31">
         <f>SUM(I7:I18)</f>
@@ -6954,16 +6977,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -6972,26 +6995,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H6" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="29" t="s">
         <v>29</v>
-      </c>
-      <c r="I6" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="L6" s="29" t="s">
-        <v>28</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>

--- a/tippmix.xlsx
+++ b/tippmix.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="70">
   <si>
     <t>♠  TIPPMIX BANKROLL MANAGER  ♠</t>
   </si>
@@ -80,6 +80,12 @@
   </si>
   <si>
     <t>psg - arsenal</t>
+  </si>
+  <si>
+    <t>psg - arsenal, magyar-dán</t>
+  </si>
+  <si>
+    <t>1, x2</t>
   </si>
   <si>
     <t>♠  TIPPMIX – HAVI ELEMZÉS</t>
@@ -3504,13 +3510,33 @@
     <row r="78" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
-      <c r="C78" s="17"/>
-      <c r="D78" s="18"/>
-      <c r="E78" s="19"/>
-      <c r="F78" s="23"/>
-      <c r="G78" s="21"/>
-      <c r="H78" s="23"/>
-      <c r="I78" s="22"/>
+      <c r="C78" s="17">
+        <v>46329.5</v>
+      </c>
+      <c r="D78" s="18">
+        <v>2000</v>
+      </c>
+      <c r="E78" s="19">
+        <v>2.5</v>
+      </c>
+      <c r="F78" s="23">
+        <f>IF(OR(E78="",D78=""),"",E78*D78)</f>
+      </c>
+      <c r="G78" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="H78" s="23">
+        <f>IF(G78="Nyert",F78,0)</f>
+      </c>
+      <c r="I78" s="22">
+        <f>IF(G78="Nyert",H78-D78,IF(G78="Veszített",-D78,0))</f>
+      </c>
+      <c r="J78" t="s">
+        <v>19</v>
+      </c>
+      <c r="K78" t="s">
+        <v>20</v>
+      </c>
       <c r="L78" s="1"/>
     </row>
     <row r="79" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -4244,7 +4270,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -4256,22 +4282,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D59)</f>
@@ -4287,7 +4313,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O4" s="44">
         <f>SUM(H7:H59)</f>
@@ -4303,7 +4329,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O5" s="44">
         <f>SUM(I7:I59)</f>
@@ -4312,16 +4338,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -4330,26 +4356,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I6" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="29" t="s">
         <v>31</v>
-      </c>
-      <c r="J6" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="L6" s="29" t="s">
-        <v>29</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>
@@ -6618,7 +6644,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6632,7 +6658,7 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="49" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B3" s="50">
         <f>SUM('Tippmix napló'!I7:I133)</f>
@@ -6643,7 +6669,7 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="49" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B4" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)</f>
@@ -6654,7 +6680,7 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="49" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B5" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))</f>
@@ -6665,7 +6691,7 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="49" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B6" s="51">
         <f>IFERROR(COUNTIF('Tippmix napló'!G7:G133,"Nyert")/(COUNTIF('Tippmix napló'!G7:G133,"Nyert")+COUNTIF('Tippmix napló'!G7:G133,"Veszített")),0)</f>
@@ -6676,7 +6702,7 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="49" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B7" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)),0)</f>
@@ -6687,7 +6713,7 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="49" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B8" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))),0)</f>
@@ -6728,7 +6754,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6746,13 +6772,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B3" s="53" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -6760,13 +6786,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="52" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B4" s="53" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -6774,13 +6800,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="52" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -6788,13 +6814,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="52" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B6" s="53" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -6802,13 +6828,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="52" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B7" s="53" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -6816,13 +6842,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="52" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B8" s="53" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -6830,13 +6856,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="52" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C9" s="54" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -6852,22 +6878,22 @@
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="55" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B12" s="55" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C12" s="56" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" ht="105" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="55"/>
       <c r="B13" s="55" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C13" s="56" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -6909,7 +6935,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6921,22 +6947,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D18)</f>
@@ -6952,7 +6978,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O4" s="31">
         <f>SUM(H7:H18)</f>
@@ -6968,7 +6994,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O5" s="31">
         <f>SUM(I7:I18)</f>
@@ -6977,16 +7003,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -6995,26 +7021,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I6" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="29" t="s">
         <v>31</v>
-      </c>
-      <c r="J6" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="L6" s="29" t="s">
-        <v>29</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>

--- a/tippmix.xlsx
+++ b/tippmix.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="72">
   <si>
     <t>♠  TIPPMIX BANKROLL MANAGER  ♠</t>
   </si>
@@ -86,6 +86,12 @@
   </si>
   <si>
     <t>1, x2</t>
+  </si>
+  <si>
+    <t>psg - arsenal, magyar-dan, foci-kosar</t>
+  </si>
+  <si>
+    <t>1,5over, 2,5over, 1x</t>
   </si>
   <si>
     <t>♠  TIPPMIX – HAVI ELEMZÉS</t>
@@ -3542,13 +3548,33 @@
     <row r="79" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
-      <c r="C79" s="17"/>
-      <c r="D79" s="18"/>
-      <c r="E79" s="19"/>
-      <c r="F79" s="20"/>
-      <c r="G79" s="21"/>
-      <c r="H79" s="20"/>
-      <c r="I79" s="22"/>
+      <c r="C79" s="17">
+        <v>46330.5</v>
+      </c>
+      <c r="D79" s="18">
+        <v>2000</v>
+      </c>
+      <c r="E79" s="19">
+        <v>2.5</v>
+      </c>
+      <c r="F79" s="20">
+        <f>IF(OR(E79="",D79=""),"",E79*D79)</f>
+      </c>
+      <c r="G79" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="H79" s="20">
+        <f>IF(G79="Nyert",F79,0)</f>
+      </c>
+      <c r="I79" s="22">
+        <f>IF(G79="Nyert",H79-D79,IF(G79="Veszített",-D79,0))</f>
+      </c>
+      <c r="J79" t="s">
+        <v>21</v>
+      </c>
+      <c r="K79" t="s">
+        <v>22</v>
+      </c>
       <c r="L79" s="1"/>
     </row>
     <row r="80" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -4270,7 +4296,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -4282,22 +4308,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D59)</f>
@@ -4313,7 +4339,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O4" s="44">
         <f>SUM(H7:H59)</f>
@@ -4329,7 +4355,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="O5" s="44">
         <f>SUM(I7:I59)</f>
@@ -4338,16 +4364,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -4356,26 +4382,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I6" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" s="29" t="s">
         <v>33</v>
-      </c>
-      <c r="J6" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="L6" s="29" t="s">
-        <v>31</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>
@@ -6644,7 +6670,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6658,7 +6684,7 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="49" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B3" s="50">
         <f>SUM('Tippmix napló'!I7:I133)</f>
@@ -6669,7 +6695,7 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="49" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B4" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)</f>
@@ -6680,7 +6706,7 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="49" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B5" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))</f>
@@ -6691,7 +6717,7 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="49" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B6" s="51">
         <f>IFERROR(COUNTIF('Tippmix napló'!G7:G133,"Nyert")/(COUNTIF('Tippmix napló'!G7:G133,"Nyert")+COUNTIF('Tippmix napló'!G7:G133,"Veszített")),0)</f>
@@ -6702,7 +6728,7 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="49" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B7" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)),0)</f>
@@ -6713,7 +6739,7 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B8" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))),0)</f>
@@ -6754,7 +6780,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6772,13 +6798,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B3" s="53" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -6786,13 +6812,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="52" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B4" s="53" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -6800,13 +6826,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="52" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -6814,13 +6840,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="52" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B6" s="53" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -6828,13 +6854,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="52" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B7" s="53" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -6842,13 +6868,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="52" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B8" s="53" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -6856,13 +6882,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="52" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C9" s="54" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -6878,22 +6904,22 @@
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="55" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B12" s="55" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C12" s="56" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" ht="105" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="55"/>
       <c r="B13" s="55" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C13" s="56" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -6935,7 +6961,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6947,22 +6973,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D18)</f>
@@ -6978,7 +7004,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O4" s="31">
         <f>SUM(H7:H18)</f>
@@ -6994,7 +7020,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="O5" s="31">
         <f>SUM(I7:I18)</f>
@@ -7003,16 +7029,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -7021,26 +7047,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I6" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" s="29" t="s">
         <v>33</v>
-      </c>
-      <c r="J6" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="L6" s="29" t="s">
-        <v>31</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>

--- a/tippmix.xlsx
+++ b/tippmix.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="70">
   <si>
     <t>♠  TIPPMIX BANKROLL MANAGER  ♠</t>
   </si>
@@ -86,12 +86,6 @@
   </si>
   <si>
     <t>1, x2</t>
-  </si>
-  <si>
-    <t>psg - arsenal, magyar-dan, foci-kosar</t>
-  </si>
-  <si>
-    <t>1,5over, 2,5over, 1x</t>
   </si>
   <si>
     <t>♠  TIPPMIX – HAVI ELEMZÉS</t>
@@ -3548,33 +3542,13 @@
     <row r="79" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
-      <c r="C79" s="17">
-        <v>46330.5</v>
-      </c>
-      <c r="D79" s="18">
-        <v>2000</v>
-      </c>
-      <c r="E79" s="19">
-        <v>2.5</v>
-      </c>
-      <c r="F79" s="20">
-        <f>IF(OR(E79="",D79=""),"",E79*D79)</f>
-      </c>
-      <c r="G79" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="H79" s="20">
-        <f>IF(G79="Nyert",F79,0)</f>
-      </c>
-      <c r="I79" s="22">
-        <f>IF(G79="Nyert",H79-D79,IF(G79="Veszített",-D79,0))</f>
-      </c>
-      <c r="J79" t="s">
-        <v>21</v>
-      </c>
-      <c r="K79" t="s">
-        <v>22</v>
-      </c>
+      <c r="C79" s="17"/>
+      <c r="D79" s="18"/>
+      <c r="E79" s="19"/>
+      <c r="F79" s="20"/>
+      <c r="G79" s="21"/>
+      <c r="H79" s="20"/>
+      <c r="I79" s="22"/>
       <c r="L79" s="1"/>
     </row>
     <row r="80" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -4296,7 +4270,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -4308,22 +4282,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D59)</f>
@@ -4339,7 +4313,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O4" s="44">
         <f>SUM(H7:H59)</f>
@@ -4355,7 +4329,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O5" s="44">
         <f>SUM(I7:I59)</f>
@@ -4364,16 +4338,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="32" t="s">
-        <v>41</v>
-      </c>
       <c r="D6" s="32" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -4382,26 +4356,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="32" t="s">
-        <v>35</v>
-      </c>
       <c r="J6" s="32" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>
@@ -6670,7 +6644,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6684,7 +6658,7 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="49" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B3" s="50">
         <f>SUM('Tippmix napló'!I7:I133)</f>
@@ -6695,7 +6669,7 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="49" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B4" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)</f>
@@ -6706,7 +6680,7 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="49" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B5" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))</f>
@@ -6717,7 +6691,7 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="49" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B6" s="51">
         <f>IFERROR(COUNTIF('Tippmix napló'!G7:G133,"Nyert")/(COUNTIF('Tippmix napló'!G7:G133,"Nyert")+COUNTIF('Tippmix napló'!G7:G133,"Veszített")),0)</f>
@@ -6728,7 +6702,7 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="49" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B7" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)),0)</f>
@@ -6739,7 +6713,7 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="49" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B8" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))),0)</f>
@@ -6780,7 +6754,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6798,13 +6772,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B3" s="53" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -6812,13 +6786,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="52" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B4" s="53" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -6826,13 +6800,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="54" t="s">
         <v>55</v>
-      </c>
-      <c r="B5" s="53" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" s="54" t="s">
-        <v>57</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -6840,13 +6814,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="52" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B6" s="53" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -6854,13 +6828,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="52" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B7" s="53" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -6868,13 +6842,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="52" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B8" s="53" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -6882,13 +6856,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="53" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="54" t="s">
         <v>64</v>
-      </c>
-      <c r="B9" s="53" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="54" t="s">
-        <v>66</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -6904,22 +6878,22 @@
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="55" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="56" t="s">
         <v>67</v>
-      </c>
-      <c r="B12" s="55" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" s="56" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="13" ht="105" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="55"/>
       <c r="B13" s="55" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C13" s="56" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -6961,7 +6935,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6973,22 +6947,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D18)</f>
@@ -7004,7 +6978,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O4" s="31">
         <f>SUM(H7:H18)</f>
@@ -7020,7 +6994,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O5" s="31">
         <f>SUM(I7:I18)</f>
@@ -7029,16 +7003,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="32" t="s">
-        <v>32</v>
-      </c>
       <c r="D6" s="32" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -7047,26 +7021,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="32" t="s">
+      <c r="J6" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="J6" s="32" t="s">
-        <v>36</v>
-      </c>
       <c r="L6" s="29" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>

--- a/tippmix.xlsx
+++ b/tippmix.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="67">
   <si>
     <t>♠  TIPPMIX BANKROLL MANAGER  ♠</t>
   </si>
@@ -77,15 +77,6 @@
   </si>
   <si>
     <t>Függőben</t>
-  </si>
-  <si>
-    <t>psg - arsenal</t>
-  </si>
-  <si>
-    <t>psg - arsenal, magyar-dán</t>
-  </si>
-  <si>
-    <t>1, x2</t>
   </si>
   <si>
     <t>♠  TIPPMIX – HAVI ELEMZÉS</t>
@@ -3478,65 +3469,25 @@
     <row r="77" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
-      <c r="C77" s="17">
-        <v>46328.5</v>
-      </c>
-      <c r="D77" s="18">
-        <v>2000</v>
-      </c>
-      <c r="E77" s="19">
-        <v>2.5</v>
-      </c>
-      <c r="F77" s="20">
-        <f>IF(OR(E77="",D77=""),"",E77*D77)</f>
-      </c>
-      <c r="G77" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="H77" s="20">
-        <f>IF(G77="Nyert",F77,0)</f>
-      </c>
-      <c r="I77" s="22">
-        <f>IF(G77="Nyert",H77-D77,IF(G77="Veszített",-D77,0))</f>
-      </c>
-      <c r="J77" t="s">
-        <v>18</v>
-      </c>
-      <c r="K77" t="s">
-        <v>15</v>
-      </c>
+      <c r="C77" s="17"/>
+      <c r="D77" s="18"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="20"/>
+      <c r="G77" s="21"/>
+      <c r="H77" s="20"/>
+      <c r="I77" s="22"/>
       <c r="L77" s="1"/>
     </row>
     <row r="78" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
-      <c r="C78" s="17">
-        <v>46329.5</v>
-      </c>
-      <c r="D78" s="18">
-        <v>2000</v>
-      </c>
-      <c r="E78" s="19">
-        <v>2.5</v>
-      </c>
-      <c r="F78" s="23">
-        <f>IF(OR(E78="",D78=""),"",E78*D78)</f>
-      </c>
-      <c r="G78" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="H78" s="23">
-        <f>IF(G78="Nyert",F78,0)</f>
-      </c>
-      <c r="I78" s="22">
-        <f>IF(G78="Nyert",H78-D78,IF(G78="Veszített",-D78,0))</f>
-      </c>
-      <c r="J78" t="s">
-        <v>19</v>
-      </c>
-      <c r="K78" t="s">
-        <v>20</v>
-      </c>
+      <c r="C78" s="17"/>
+      <c r="D78" s="18"/>
+      <c r="E78" s="19"/>
+      <c r="F78" s="23"/>
+      <c r="G78" s="21"/>
+      <c r="H78" s="23"/>
+      <c r="I78" s="22"/>
       <c r="L78" s="1"/>
     </row>
     <row r="79" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -4270,7 +4221,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -4282,22 +4233,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D59)</f>
@@ -4313,7 +4264,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O4" s="44">
         <f>SUM(H7:H59)</f>
@@ -4329,7 +4280,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O5" s="44">
         <f>SUM(I7:I59)</f>
@@ -4338,16 +4289,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -4356,26 +4307,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="I6" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="J6" s="32" t="s">
-        <v>34</v>
-      </c>
       <c r="L6" s="29" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>
@@ -6644,7 +6595,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6658,7 +6609,7 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="49" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B3" s="50">
         <f>SUM('Tippmix napló'!I7:I133)</f>
@@ -6669,7 +6620,7 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="49" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B4" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)</f>
@@ -6680,7 +6631,7 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="49" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B5" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))</f>
@@ -6691,7 +6642,7 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="49" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B6" s="51">
         <f>IFERROR(COUNTIF('Tippmix napló'!G7:G133,"Nyert")/(COUNTIF('Tippmix napló'!G7:G133,"Nyert")+COUNTIF('Tippmix napló'!G7:G133,"Veszített")),0)</f>
@@ -6702,7 +6653,7 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="49" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B7" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)),0)</f>
@@ -6713,7 +6664,7 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="49" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B8" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))),0)</f>
@@ -6754,7 +6705,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6772,13 +6723,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B3" s="53" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -6786,13 +6737,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="52" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B4" s="53" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -6800,13 +6751,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="52" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -6814,13 +6765,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="52" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B6" s="53" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -6828,13 +6779,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="52" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B7" s="53" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -6842,13 +6793,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="52" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B8" s="53" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -6856,13 +6807,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="52" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C9" s="54" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -6878,22 +6829,22 @@
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="55" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B12" s="55" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C12" s="56" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" ht="105" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="55"/>
       <c r="B13" s="55" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C13" s="56" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -6935,7 +6886,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6947,22 +6898,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D18)</f>
@@ -6978,7 +6929,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O4" s="31">
         <f>SUM(H7:H18)</f>
@@ -6994,7 +6945,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O5" s="31">
         <f>SUM(I7:I18)</f>
@@ -7003,16 +6954,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -7021,26 +6972,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="J6" s="32" t="s">
-        <v>34</v>
-      </c>
       <c r="L6" s="29" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>

--- a/tippmix.xlsx
+++ b/tippmix.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="67">
   <si>
     <t>♠  TIPPMIX BANKROLL MANAGER  ♠</t>
   </si>
@@ -3469,13 +3469,33 @@
     <row r="77" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
-      <c r="C77" s="17"/>
-      <c r="D77" s="18"/>
-      <c r="E77" s="19"/>
-      <c r="F77" s="20"/>
-      <c r="G77" s="21"/>
-      <c r="H77" s="20"/>
-      <c r="I77" s="22"/>
+      <c r="C77" s="17">
+        <v>46328.5</v>
+      </c>
+      <c r="D77" s="18">
+        <v>2000</v>
+      </c>
+      <c r="E77" s="19">
+        <v>2.5</v>
+      </c>
+      <c r="F77" s="20">
+        <f>IF(OR(E77="",D77=""),"",E77*D77)</f>
+      </c>
+      <c r="G77" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="H77" s="20">
+        <f>IF(G77="Nyert",F77,0)</f>
+      </c>
+      <c r="I77" s="22">
+        <f>IF(G77="Nyert",H77-D77,IF(G77="Veszített",-D77,0))</f>
+      </c>
+      <c r="J77" t="s">
+        <v>15</v>
+      </c>
+      <c r="K77" t="s">
+        <v>15</v>
+      </c>
       <c r="L77" s="1"/>
     </row>
     <row r="78" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">

--- a/tippmix.xlsx
+++ b/tippmix.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="67">
   <si>
     <t>♠  TIPPMIX BANKROLL MANAGER  ♠</t>
   </si>
@@ -3470,7 +3470,7 @@
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="17">
-        <v>46328.5</v>
+        <v>46324.5</v>
       </c>
       <c r="D77" s="18">
         <v>2000</v>
@@ -3501,13 +3501,33 @@
     <row r="78" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
-      <c r="C78" s="17"/>
-      <c r="D78" s="18"/>
-      <c r="E78" s="19"/>
-      <c r="F78" s="23"/>
-      <c r="G78" s="21"/>
-      <c r="H78" s="23"/>
-      <c r="I78" s="22"/>
+      <c r="C78" s="17">
+        <v>46328.5</v>
+      </c>
+      <c r="D78" s="18">
+        <v>2000</v>
+      </c>
+      <c r="E78" s="19">
+        <v>2.5</v>
+      </c>
+      <c r="F78" s="23">
+        <f>IF(OR(E78="",D78=""),"",E78*D78)</f>
+      </c>
+      <c r="G78" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="H78" s="23">
+        <f>IF(G78="Nyert",F78,0)</f>
+      </c>
+      <c r="I78" s="22">
+        <f>IF(G78="Nyert",H78-D78,IF(G78="Veszített",-D78,0))</f>
+      </c>
+      <c r="J78" t="s">
+        <v>15</v>
+      </c>
+      <c r="K78" t="s">
+        <v>15</v>
+      </c>
       <c r="L78" s="1"/>
     </row>
     <row r="79" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">

--- a/tippmix.xlsx
+++ b/tippmix.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="69">
   <si>
     <t>♠  TIPPMIX BANKROLL MANAGER  ♠</t>
   </si>
@@ -77,6 +77,12 @@
   </si>
   <si>
     <t>Függőben</t>
+  </si>
+  <si>
+    <t>gabibuzi</t>
+  </si>
+  <si>
+    <t>az igen</t>
   </si>
   <si>
     <t>♠  TIPPMIX – HAVI ELEMZÉS</t>
@@ -3502,7 +3508,7 @@
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="17">
-        <v>46328.5</v>
+        <v>46324.5</v>
       </c>
       <c r="D78" s="18">
         <v>2000</v>
@@ -3523,23 +3529,43 @@
         <f>IF(G78="Nyert",H78-D78,IF(G78="Veszített",-D78,0))</f>
       </c>
       <c r="J78" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K78" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L78" s="1"/>
     </row>
     <row r="79" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
-      <c r="C79" s="17"/>
-      <c r="D79" s="18"/>
-      <c r="E79" s="19"/>
-      <c r="F79" s="20"/>
-      <c r="G79" s="21"/>
-      <c r="H79" s="20"/>
-      <c r="I79" s="22"/>
+      <c r="C79" s="17">
+        <v>46328.5</v>
+      </c>
+      <c r="D79" s="18">
+        <v>2000</v>
+      </c>
+      <c r="E79" s="19">
+        <v>2.5</v>
+      </c>
+      <c r="F79" s="20">
+        <f>IF(OR(E79="",D79=""),"",E79*D79)</f>
+      </c>
+      <c r="G79" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="H79" s="20">
+        <f>IF(G79="Nyert",F79,0)</f>
+      </c>
+      <c r="I79" s="22">
+        <f>IF(G79="Nyert",H79-D79,IF(G79="Veszített",-D79,0))</f>
+      </c>
+      <c r="J79" t="s">
+        <v>15</v>
+      </c>
+      <c r="K79" t="s">
+        <v>15</v>
+      </c>
       <c r="L79" s="1"/>
     </row>
     <row r="80" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -4261,7 +4287,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -4273,22 +4299,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D59)</f>
@@ -4304,7 +4330,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O4" s="44">
         <f>SUM(H7:H59)</f>
@@ -4320,7 +4346,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O5" s="44">
         <f>SUM(I7:I59)</f>
@@ -4329,16 +4355,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -4347,26 +4373,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I6" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="29" t="s">
         <v>30</v>
-      </c>
-      <c r="J6" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="L6" s="29" t="s">
-        <v>28</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>
@@ -6635,7 +6661,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6649,7 +6675,7 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="49" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B3" s="50">
         <f>SUM('Tippmix napló'!I7:I133)</f>
@@ -6660,7 +6686,7 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="49" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)</f>
@@ -6671,7 +6697,7 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="49" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B5" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))</f>
@@ -6682,7 +6708,7 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="49" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B6" s="51">
         <f>IFERROR(COUNTIF('Tippmix napló'!G7:G133,"Nyert")/(COUNTIF('Tippmix napló'!G7:G133,"Nyert")+COUNTIF('Tippmix napló'!G7:G133,"Veszített")),0)</f>
@@ -6693,7 +6719,7 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="49" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B7" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)),0)</f>
@@ -6704,7 +6730,7 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="49" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B8" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))),0)</f>
@@ -6745,7 +6771,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6763,13 +6789,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B3" s="53" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -6777,13 +6803,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="52" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B4" s="53" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -6791,13 +6817,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="52" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -6805,13 +6831,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="52" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B6" s="53" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -6819,13 +6845,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="52" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B7" s="53" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -6833,13 +6859,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="52" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B8" s="53" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -6847,13 +6873,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="52" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C9" s="54" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -6869,22 +6895,22 @@
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="55" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B12" s="55" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C12" s="56" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" ht="105" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="55"/>
       <c r="B13" s="55" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C13" s="56" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -6926,7 +6952,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6938,22 +6964,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D18)</f>
@@ -6969,7 +6995,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O4" s="31">
         <f>SUM(H7:H18)</f>
@@ -6985,7 +7011,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O5" s="31">
         <f>SUM(I7:I18)</f>
@@ -6994,16 +7020,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -7012,26 +7038,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I6" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="29" t="s">
         <v>30</v>
-      </c>
-      <c r="J6" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="L6" s="29" t="s">
-        <v>28</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>

--- a/tippmix.xlsx
+++ b/tippmix.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="69">
   <si>
     <t>♠  TIPPMIX BANKROLL MANAGER  ♠</t>
   </si>
@@ -3539,33 +3539,13 @@
     <row r="79" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
-      <c r="C79" s="17">
-        <v>46328.5</v>
-      </c>
-      <c r="D79" s="18">
-        <v>2000</v>
-      </c>
-      <c r="E79" s="19">
-        <v>2.5</v>
-      </c>
-      <c r="F79" s="20">
-        <f>IF(OR(E79="",D79=""),"",E79*D79)</f>
-      </c>
-      <c r="G79" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="H79" s="20">
-        <f>IF(G79="Nyert",F79,0)</f>
-      </c>
-      <c r="I79" s="22">
-        <f>IF(G79="Nyert",H79-D79,IF(G79="Veszített",-D79,0))</f>
-      </c>
-      <c r="J79" t="s">
-        <v>15</v>
-      </c>
-      <c r="K79" t="s">
-        <v>15</v>
-      </c>
+      <c r="C79" s="17"/>
+      <c r="D79" s="18"/>
+      <c r="E79" s="19"/>
+      <c r="F79" s="20"/>
+      <c r="G79" s="21"/>
+      <c r="H79" s="20"/>
+      <c r="I79" s="22"/>
       <c r="L79" s="1"/>
     </row>
     <row r="80" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">

--- a/tippmix.xlsx
+++ b/tippmix.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="69">
   <si>
     <t>♠  TIPPMIX BANKROLL MANAGER  ♠</t>
   </si>
@@ -3497,43 +3497,23 @@
         <f>IF(G77="Nyert",H77-D77,IF(G77="Veszített",-D77,0))</f>
       </c>
       <c r="J77" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K77" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L77" s="1"/>
     </row>
     <row r="78" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
-      <c r="C78" s="17">
-        <v>46324.5</v>
-      </c>
-      <c r="D78" s="18">
-        <v>2000</v>
-      </c>
-      <c r="E78" s="19">
-        <v>2.5</v>
-      </c>
-      <c r="F78" s="23">
-        <f>IF(OR(E78="",D78=""),"",E78*D78)</f>
-      </c>
-      <c r="G78" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="H78" s="23">
-        <f>IF(G78="Nyert",F78,0)</f>
-      </c>
-      <c r="I78" s="22">
-        <f>IF(G78="Nyert",H78-D78,IF(G78="Veszített",-D78,0))</f>
-      </c>
-      <c r="J78" t="s">
-        <v>18</v>
-      </c>
-      <c r="K78" t="s">
-        <v>19</v>
-      </c>
+      <c r="C78" s="17"/>
+      <c r="D78" s="18"/>
+      <c r="E78" s="19"/>
+      <c r="F78" s="23"/>
+      <c r="G78" s="21"/>
+      <c r="H78" s="23"/>
+      <c r="I78" s="22"/>
       <c r="L78" s="1"/>
     </row>
     <row r="79" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">

--- a/tippmix.xlsx
+++ b/tippmix.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="67">
   <si>
     <t>♠  TIPPMIX BANKROLL MANAGER  ♠</t>
   </si>
@@ -77,12 +77,6 @@
   </si>
   <si>
     <t>Függőben</t>
-  </si>
-  <si>
-    <t>gabibuzi</t>
-  </si>
-  <si>
-    <t>az igen</t>
   </si>
   <si>
     <t>♠  TIPPMIX – HAVI ELEMZÉS</t>
@@ -3475,33 +3469,13 @@
     <row r="77" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
-      <c r="C77" s="17">
-        <v>46324.5</v>
-      </c>
-      <c r="D77" s="18">
-        <v>2000</v>
-      </c>
-      <c r="E77" s="19">
-        <v>2.5</v>
-      </c>
-      <c r="F77" s="20">
-        <f>IF(OR(E77="",D77=""),"",E77*D77)</f>
-      </c>
-      <c r="G77" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="H77" s="20">
-        <f>IF(G77="Nyert",F77,0)</f>
-      </c>
-      <c r="I77" s="22">
-        <f>IF(G77="Nyert",H77-D77,IF(G77="Veszített",-D77,0))</f>
-      </c>
-      <c r="J77" t="s">
-        <v>18</v>
-      </c>
-      <c r="K77" t="s">
-        <v>19</v>
-      </c>
+      <c r="C77" s="17"/>
+      <c r="D77" s="18"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="20"/>
+      <c r="G77" s="21"/>
+      <c r="H77" s="20"/>
+      <c r="I77" s="22"/>
       <c r="L77" s="1"/>
     </row>
     <row r="78" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -4247,7 +4221,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -4259,22 +4233,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D59)</f>
@@ -4290,7 +4264,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="O4" s="44">
         <f>SUM(H7:H59)</f>
@@ -4306,7 +4280,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="O5" s="44">
         <f>SUM(I7:I59)</f>
@@ -4315,16 +4289,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="32" t="s">
-        <v>38</v>
-      </c>
       <c r="D6" s="32" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -4333,26 +4307,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="I6" s="32" t="s">
-        <v>32</v>
-      </c>
       <c r="J6" s="32" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>
@@ -6621,7 +6595,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6635,7 +6609,7 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="49" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B3" s="50">
         <f>SUM('Tippmix napló'!I7:I133)</f>
@@ -6646,7 +6620,7 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="49" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B4" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)</f>
@@ -6657,7 +6631,7 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="49" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B5" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))</f>
@@ -6668,7 +6642,7 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="49" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B6" s="51">
         <f>IFERROR(COUNTIF('Tippmix napló'!G7:G133,"Nyert")/(COUNTIF('Tippmix napló'!G7:G133,"Nyert")+COUNTIF('Tippmix napló'!G7:G133,"Veszített")),0)</f>
@@ -6679,7 +6653,7 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="49" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B7" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)),0)</f>
@@ -6690,7 +6664,7 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="49" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B8" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))),0)</f>
@@ -6731,7 +6705,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6749,13 +6723,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B3" s="53" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -6763,13 +6737,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="52" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B4" s="53" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -6777,13 +6751,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="52" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="53" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="54" t="s">
         <v>52</v>
-      </c>
-      <c r="B5" s="53" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" s="54" t="s">
-        <v>54</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -6791,13 +6765,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="52" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B6" s="53" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -6805,13 +6779,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="52" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B7" s="53" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -6819,13 +6793,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="52" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B8" s="53" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -6833,13 +6807,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="54" t="s">
         <v>61</v>
-      </c>
-      <c r="B9" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" s="54" t="s">
-        <v>63</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -6855,22 +6829,22 @@
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="55" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="56" t="s">
         <v>64</v>
-      </c>
-      <c r="B12" s="55" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="56" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="13" ht="105" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="55"/>
       <c r="B13" s="55" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C13" s="56" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -6912,7 +6886,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6924,22 +6898,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D18)</f>
@@ -6955,7 +6929,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="O4" s="31">
         <f>SUM(H7:H18)</f>
@@ -6971,7 +6945,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="O5" s="31">
         <f>SUM(I7:I18)</f>
@@ -6980,16 +6954,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="32" t="s">
-        <v>29</v>
-      </c>
       <c r="D6" s="32" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -6998,26 +6972,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="32" t="s">
+      <c r="J6" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="I6" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" s="32" t="s">
-        <v>33</v>
-      </c>
       <c r="L6" s="29" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>

--- a/tippmix.xlsx
+++ b/tippmix.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="67">
   <si>
     <t>♠  TIPPMIX BANKROLL MANAGER  ♠</t>
   </si>
@@ -3469,13 +3469,33 @@
     <row r="77" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
-      <c r="C77" s="17"/>
-      <c r="D77" s="18"/>
-      <c r="E77" s="19"/>
-      <c r="F77" s="20"/>
-      <c r="G77" s="21"/>
-      <c r="H77" s="20"/>
-      <c r="I77" s="22"/>
+      <c r="C77" s="17">
+        <v>46325.5</v>
+      </c>
+      <c r="D77" s="18">
+        <v>2000</v>
+      </c>
+      <c r="E77" s="19">
+        <v>2.54</v>
+      </c>
+      <c r="F77" s="20">
+        <f>IF(OR(E77="",D77=""),"",E77*D77)</f>
+      </c>
+      <c r="G77" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="H77" s="20">
+        <f>IF(G77="Nyert",F77,0)</f>
+      </c>
+      <c r="I77" s="22">
+        <f>IF(G77="Nyert",H77-D77,IF(G77="Veszített",-D77,0))</f>
+      </c>
+      <c r="J77" t="s">
+        <v>15</v>
+      </c>
+      <c r="K77" t="s">
+        <v>15</v>
+      </c>
       <c r="L77" s="1"/>
     </row>
     <row r="78" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">

--- a/tippmix.xlsx
+++ b/tippmix.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="67">
   <si>
     <t>♠  TIPPMIX BANKROLL MANAGER  ♠</t>
   </si>
@@ -3438,13 +3438,13 @@
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="17">
-        <v>46324.5</v>
+        <v>46325.5</v>
       </c>
       <c r="D76" s="18">
         <v>2000</v>
       </c>
       <c r="E76" s="19">
-        <v>2.2</v>
+        <v>2.54</v>
       </c>
       <c r="F76" s="23">
         <f>IF(OR(E76="",D76=""),"",E76*D76)</f>
@@ -3469,33 +3469,13 @@
     <row r="77" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
-      <c r="C77" s="17">
-        <v>46325.5</v>
-      </c>
-      <c r="D77" s="18">
-        <v>2000</v>
-      </c>
-      <c r="E77" s="19">
-        <v>2.54</v>
-      </c>
-      <c r="F77" s="20">
-        <f>IF(OR(E77="",D77=""),"",E77*D77)</f>
-      </c>
-      <c r="G77" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="H77" s="20">
-        <f>IF(G77="Nyert",F77,0)</f>
-      </c>
-      <c r="I77" s="22">
-        <f>IF(G77="Nyert",H77-D77,IF(G77="Veszített",-D77,0))</f>
-      </c>
-      <c r="J77" t="s">
-        <v>15</v>
-      </c>
-      <c r="K77" t="s">
-        <v>15</v>
-      </c>
+      <c r="C77" s="17"/>
+      <c r="D77" s="18"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="20"/>
+      <c r="G77" s="21"/>
+      <c r="H77" s="20"/>
+      <c r="I77" s="22"/>
       <c r="L77" s="1"/>
     </row>
     <row r="78" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">

--- a/tippmix.xlsx
+++ b/tippmix.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="66">
   <si>
     <t>♠  TIPPMIX BANKROLL MANAGER  ♠</t>
   </si>
@@ -74,9 +74,6 @@
   </si>
   <si>
     <t>Veszített</t>
-  </si>
-  <si>
-    <t>Függőben</t>
   </si>
   <si>
     <t>♠  TIPPMIX – HAVI ELEMZÉS</t>
@@ -3450,7 +3447,7 @@
         <f>IF(OR(E76="",D76=""),"",E76*D76)</f>
       </c>
       <c r="G76" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H76" s="23">
         <f>IF(G76="Nyert",F76,0)</f>
@@ -4221,7 +4218,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -4233,22 +4230,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D59)</f>
@@ -4264,7 +4261,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O4" s="44">
         <f>SUM(H7:H59)</f>
@@ -4280,7 +4277,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O5" s="44">
         <f>SUM(I7:I59)</f>
@@ -4289,16 +4286,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="C6" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="32" t="s">
-        <v>36</v>
-      </c>
       <c r="D6" s="32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -4307,26 +4304,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I6" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="32" t="s">
-        <v>31</v>
-      </c>
       <c r="L6" s="29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>
@@ -6595,7 +6592,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6609,7 +6606,7 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="50">
         <f>SUM('Tippmix napló'!I7:I133)</f>
@@ -6620,7 +6617,7 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)</f>
@@ -6631,7 +6628,7 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))</f>
@@ -6642,7 +6639,7 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B6" s="51">
         <f>IFERROR(COUNTIF('Tippmix napló'!G7:G133,"Nyert")/(COUNTIF('Tippmix napló'!G7:G133,"Nyert")+COUNTIF('Tippmix napló'!G7:G133,"Veszített")),0)</f>
@@ -6653,7 +6650,7 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="49" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B7" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)),0)</f>
@@ -6664,7 +6661,7 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="49" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B8" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))),0)</f>
@@ -6705,7 +6702,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6723,13 +6720,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B3" s="53" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -6737,13 +6734,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="52" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B4" s="53" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -6751,13 +6748,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="52" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="53" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="C5" s="54" t="s">
         <v>51</v>
-      </c>
-      <c r="C5" s="54" t="s">
-        <v>52</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -6765,13 +6762,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="52" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" s="53" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -6779,13 +6776,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="52" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B7" s="53" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -6793,13 +6790,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="52" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B8" s="53" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -6807,13 +6804,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="53" t="s">
+      <c r="C9" s="54" t="s">
         <v>60</v>
-      </c>
-      <c r="C9" s="54" t="s">
-        <v>61</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -6829,22 +6826,22 @@
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="55" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="55" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="55" t="s">
+      <c r="C12" s="56" t="s">
         <v>63</v>
-      </c>
-      <c r="C12" s="56" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="13" ht="105" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="55"/>
       <c r="B13" s="55" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="56" t="s">
         <v>65</v>
-      </c>
-      <c r="C13" s="56" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -6886,7 +6883,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6898,22 +6895,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="29" t="s">
         <v>21</v>
-      </c>
-      <c r="L3" s="29" t="s">
-        <v>22</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D18)</f>
@@ -6929,7 +6926,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O4" s="31">
         <f>SUM(H7:H18)</f>
@@ -6945,7 +6942,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O5" s="31">
         <f>SUM(I7:I18)</f>
@@ -6954,16 +6951,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="C6" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="32" t="s">
-        <v>27</v>
-      </c>
       <c r="D6" s="32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -6972,26 +6969,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="32" t="s">
+      <c r="I6" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="32" t="s">
+      <c r="J6" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="32" t="s">
-        <v>31</v>
-      </c>
       <c r="L6" s="29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>

--- a/tippmix.xlsx
+++ b/tippmix.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="67">
   <si>
     <t>♠  TIPPMIX BANKROLL MANAGER  ♠</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t>Veszített</t>
+  </si>
+  <si>
+    <t>Függőben</t>
   </si>
   <si>
     <t>♠  TIPPMIX – HAVI ELEMZÉS</t>
@@ -3466,13 +3469,33 @@
     <row r="77" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
-      <c r="C77" s="17"/>
-      <c r="D77" s="18"/>
-      <c r="E77" s="19"/>
-      <c r="F77" s="20"/>
-      <c r="G77" s="21"/>
-      <c r="H77" s="20"/>
-      <c r="I77" s="22"/>
+      <c r="C77" s="17">
+        <v>46326.5</v>
+      </c>
+      <c r="D77" s="18">
+        <v>2000</v>
+      </c>
+      <c r="E77" s="19">
+        <v>2.67</v>
+      </c>
+      <c r="F77" s="20">
+        <f>IF(OR(E77="",D77=""),"",E77*D77)</f>
+      </c>
+      <c r="G77" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="H77" s="20">
+        <f>IF(G77="Nyert",F77,0)</f>
+      </c>
+      <c r="I77" s="22">
+        <f>IF(G77="Nyert",H77-D77,IF(G77="Veszített",-D77,0))</f>
+      </c>
+      <c r="J77" t="s">
+        <v>15</v>
+      </c>
+      <c r="K77" t="s">
+        <v>15</v>
+      </c>
       <c r="L77" s="1"/>
     </row>
     <row r="78" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -4218,7 +4241,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -4230,22 +4253,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D59)</f>
@@ -4261,7 +4284,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O4" s="44">
         <f>SUM(H7:H59)</f>
@@ -4277,7 +4300,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O5" s="44">
         <f>SUM(I7:I59)</f>
@@ -4286,16 +4309,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -4304,26 +4327,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J6" s="32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>
@@ -6592,7 +6615,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6606,7 +6629,7 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="49" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="50">
         <f>SUM('Tippmix napló'!I7:I133)</f>
@@ -6617,7 +6640,7 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="49" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)</f>
@@ -6628,7 +6651,7 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="49" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="50">
         <f>SUMIFS('Tippmix napló'!I7:I133,'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))</f>
@@ -6639,7 +6662,7 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="49" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6" s="51">
         <f>IFERROR(COUNTIF('Tippmix napló'!G7:G133,"Nyert")/(COUNTIF('Tippmix napló'!G7:G133,"Nyert")+COUNTIF('Tippmix napló'!G7:G133,"Veszített")),0)</f>
@@ -6650,7 +6673,7 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="49" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1,'Tippmix napló'!C7:C133,"&lt;"&amp;TODAY()-WEEKDAY(TODAY(),2)+8)),0)</f>
@@ -6661,7 +6684,7 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="49" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8" s="51">
         <f>IFERROR(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))/(COUNTIFS('Tippmix napló'!G7:G133,"Nyert",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))+COUNTIFS('Tippmix napló'!G7:G133,"Veszített",'Tippmix napló'!C7:C133,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,'Tippmix napló'!C7:C133,"&lt;="&amp;EOMONTH(TODAY(),0))),0)</f>
@@ -6702,7 +6725,7 @@
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6720,13 +6743,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B3" s="53" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -6734,13 +6757,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="52" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B4" s="53" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -6748,13 +6771,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="52" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -6762,13 +6785,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="52" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" s="53" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -6776,13 +6799,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="52" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B7" s="53" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -6790,13 +6813,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="52" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B8" s="53" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -6804,13 +6827,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="52" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C9" s="54" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -6826,22 +6849,22 @@
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="55" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B12" s="55" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C12" s="56" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" ht="105" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="55"/>
       <c r="B13" s="55" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C13" s="56" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -6883,7 +6906,7 @@
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6895,22 +6918,22 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="L1" s="25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="27">
         <v>2026</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M3" s="30">
         <f>SUM(D7:D18)</f>
@@ -6926,7 +6949,7 @@
         <v>40</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O4" s="31">
         <f>SUM(H7:H18)</f>
@@ -6942,7 +6965,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O5" s="31">
         <f>SUM(I7:I18)</f>
@@ -6951,16 +6974,16 @@
     </row>
     <row r="6" ht="32.1" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="32" t="s">
         <v>14</v>
@@ -6969,26 +6992,26 @@
         <v>16</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H6" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="L6" s="29" t="s">
         <v>28</v>
-      </c>
-      <c r="I6" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="29" t="s">
-        <v>27</v>
       </c>
       <c r="M6" s="33">
         <f>IFERROR(M4/M3,0)</f>
         <v>0.6060606060606061</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O6" s="33">
         <f>IFERROR(O4/O5,0)</f>

--- a/tippmix.xlsx
+++ b/tippmix.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="67">
   <si>
     <t>♠  TIPPMIX BANKROLL MANAGER  ♠</t>
   </si>
@@ -3501,13 +3501,33 @@
     <row r="78" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
-      <c r="C78" s="17"/>
-      <c r="D78" s="18"/>
-      <c r="E78" s="19"/>
-      <c r="F78" s="23"/>
-      <c r="G78" s="21"/>
-      <c r="H78" s="23"/>
-      <c r="I78" s="22"/>
+      <c r="C78" s="17">
+        <v>46326.5</v>
+      </c>
+      <c r="D78" s="18">
+        <v>2000</v>
+      </c>
+      <c r="E78" s="19">
+        <v>2.67</v>
+      </c>
+      <c r="F78" s="23">
+        <f>IF(OR(E78="",D78=""),"",E78*D78)</f>
+      </c>
+      <c r="G78" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="H78" s="23">
+        <f>IF(G78="Nyert",F78,0)</f>
+      </c>
+      <c r="I78" s="22">
+        <f>IF(G78="Nyert",H78-D78,IF(G78="Veszített",-D78,0))</f>
+      </c>
+      <c r="J78" t="s">
+        <v>15</v>
+      </c>
+      <c r="K78" t="s">
+        <v>15</v>
+      </c>
       <c r="L78" s="1"/>
     </row>
     <row r="79" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
